--- a/test/excel/keep/struct-open/print-insert.xlsx
+++ b/test/excel/keep/struct-open/print-insert.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-38154/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-77939/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8425F7F-52C0-2047-917D-8837B7B2407F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D693B3DD-A1F9-5548-81D8-1D8115552DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="14">
   <si>
     <t>Region</t>
   </si>
@@ -110,18 +110,38 @@
       <t>t</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>outh</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,7 +187,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -822,7 +842,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>35</v>
